--- a/hall/resources/sample/jumpData.xlsx
+++ b/hall/resources/sample/jumpData.xlsx
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
   <si>
     <t>跳转ID</t>
   </si>
@@ -145,6 +145,18 @@
     <t>金矿大亨</t>
   </si>
   <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
     <t>创建房间</t>
   </si>
   <si>
@@ -169,24 +181,36 @@
     <t>UIDailyBonus</t>
   </si>
   <si>
+    <t>每日奖金</t>
+  </si>
+  <si>
     <t>活动-摇钱树-常驻</t>
   </si>
   <si>
     <t>UICashCow</t>
   </si>
   <si>
+    <t>摇钱树</t>
+  </si>
+  <si>
     <t>活动-储钱罐-常驻</t>
   </si>
   <si>
     <t>UISavingPot</t>
   </si>
   <si>
+    <t>储钱罐</t>
+  </si>
+  <si>
     <t>活动-刮刮卡-常驻</t>
   </si>
   <si>
     <t>UIScratchCards</t>
   </si>
   <si>
+    <t>刮刮卡</t>
+  </si>
+  <si>
     <t>游戏</t>
   </si>
   <si>
@@ -200,18 +224,6 @@
   </si>
   <si>
     <t>金礦大亨</t>
-  </si>
-  <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>麻将胡了</t>
-  </si>
-  <si>
-    <t>财神</t>
-  </si>
-  <si>
-    <t>埃及艳后</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -1457,7 +1469,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1471,7 +1483,7 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1488,7 +1500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1503,7 +1515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -1518,7 +1530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="6:9">
+    <row r="4" spans="1:9">
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4"/>
@@ -1526,7 +1538,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4">
-        <v>1001</v>
+        <v>11001</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>11</v>
@@ -1537,140 +1549,225 @@
       <c r="D5" s="1">
         <v>100100</v>
       </c>
-      <c r="F5"/>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
       <c r="G5"/>
       <c r="H5"/>
       <c r="I5"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="5">
-        <v>2001</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="4">
+        <v>11003</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6"/>
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>100300</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="5">
-        <v>2002</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
+      <c r="A7" s="4">
+        <v>11007</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>100700</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7"/>
       <c r="H7"/>
       <c r="I7"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="5">
-        <v>2003</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>16</v>
+      <c r="A8" s="4">
+        <v>11012</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>101200</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8"/>
       <c r="H8"/>
       <c r="I8"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6">
-        <v>3001</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>18</v>
+      <c r="A9" s="4">
+        <v>11014</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9"/>
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>101400</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
       <c r="G9"/>
       <c r="H9"/>
       <c r="I9"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6">
-        <v>3002</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>20</v>
+      <c r="A10" s="5">
+        <v>2001</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C10" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10"/>
       <c r="H10"/>
       <c r="I10"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6">
-        <v>3003</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>22</v>
+      <c r="A11" s="5">
+        <v>2002</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6">
-        <v>3004</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>24</v>
+      <c r="A12" s="5">
+        <v>2003</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="8:9">
+    <row r="13" spans="1:9">
+      <c r="A13" s="6">
+        <v>3001</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="8:9">
+    <row r="14" spans="1:9">
+      <c r="A14" s="6">
+        <v>3002</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="8:9">
+    <row r="15" spans="1:9">
+      <c r="A15" s="6">
+        <v>3003</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="8:9">
+    <row r="16" spans="1:9">
+      <c r="A16" s="6">
+        <v>3004</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="H16"/>
       <c r="I16"/>
     </row>
@@ -1713,6 +1810,22 @@
     <row r="26" spans="8:9">
       <c r="H26"/>
       <c r="I26"/>
+    </row>
+    <row r="27" spans="8:9">
+      <c r="H27"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="8:9">
+      <c r="H28"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="8:9">
+      <c r="H29"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="8:9">
+      <c r="H30"/>
+      <c r="I30"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1742,7 +1855,7 @@
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:12">
       <c r="B1" s="1">
         <v>1</v>
       </c>
@@ -1755,185 +1868,185 @@
     </row>
     <row r="2" spans="2:12">
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="3:12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
       <c r="C3" s="1">
         <v>100100</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K3" s="1">
         <v>2</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
       <c r="C4" s="1">
         <v>100300</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K4" s="1">
         <v>3</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
       <c r="C5" s="1">
         <v>100700</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K5" s="1">
         <v>4</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
       <c r="C6" s="1">
         <v>101200</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K6" s="1">
         <v>5</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
       <c r="C7" s="1">
         <v>101400</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
       <c r="C8" s="1">
         <v>200100</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
       <c r="C9" s="1">
         <v>200101</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="3:4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
       <c r="C10" s="1">
         <v>200300</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="3:4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
       <c r="C11" s="1">
         <v>200400</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
       <c r="C12" s="1">
         <v>200500</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
       <c r="C13" s="1">
         <v>200600</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="3:4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
       <c r="C14" s="1">
         <v>200700</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="3:4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
       <c r="C15" s="1">
         <v>200800</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="3:4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
       <c r="C16" s="1">
         <v>200900</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="3:4">
@@ -1941,7 +2054,7 @@
         <v>201000</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="3:4">
@@ -1949,7 +2062,7 @@
         <v>300100</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="3:4">
@@ -1957,7 +2070,7 @@
         <v>300200</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
